--- a/evaluation/evaluation_labels_only.xlsx
+++ b/evaluation/evaluation_labels_only.xlsx
@@ -830,7 +830,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -840,13 +840,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -904,7 +898,7 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1218,8 +1212,8 @@
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="59.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="41.005" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -1231,7 +1225,7 @@
     <col min="11" max="11" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1266,7 +1260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="45.75">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1301,7 +1295,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -1336,7 +1330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="138">
       <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
@@ -1371,7 +1365,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="84.75">
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
@@ -1406,7 +1400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="243.75">
       <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
@@ -1441,7 +1435,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="45.75">
       <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
@@ -1476,7 +1470,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="45.75">
       <c r="A8" s="3" t="s">
         <v>43</v>
       </c>
@@ -1511,7 +1505,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="45.75">
       <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
@@ -1546,7 +1540,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="375.75">
       <c r="A10" s="3" t="s">
         <v>53</v>
       </c>
@@ -1581,7 +1575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="150.75">
       <c r="A11" s="3" t="s">
         <v>58</v>
       </c>
@@ -1616,7 +1610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="270">
       <c r="A12" s="3" t="s">
         <v>63</v>
       </c>
@@ -1651,7 +1645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="124.5">
       <c r="A13" s="3" t="s">
         <v>68</v>
       </c>
@@ -1686,7 +1680,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="84.75">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -1721,7 +1715,7 @@
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="164.25">
       <c r="A15" s="3" t="s">
         <v>79</v>
       </c>
@@ -1756,7 +1750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="98.25">
       <c r="A16" s="3" t="s">
         <v>84</v>
       </c>
@@ -1791,7 +1785,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="58.5">
       <c r="A17" s="3" t="s">
         <v>89</v>
       </c>
@@ -1826,7 +1820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="84.75">
       <c r="A18" s="3" t="s">
         <v>94</v>
       </c>
@@ -1861,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="138">
       <c r="A19" s="3" t="s">
         <v>99</v>
       </c>
@@ -1896,7 +1890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="138">
       <c r="A20" s="3" t="s">
         <v>104</v>
       </c>
@@ -1931,7 +1925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="138">
       <c r="A21" s="3" t="s">
         <v>109</v>
       </c>
@@ -1966,7 +1960,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="111.75">
       <c r="A22" s="3" t="s">
         <v>114</v>
       </c>
@@ -2001,7 +1995,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="45.75">
       <c r="A23" s="3" t="s">
         <v>119</v>
       </c>

--- a/evaluation/evaluation_labels_only.xlsx
+++ b/evaluation/evaluation_labels_only.xlsx
@@ -2030,7 +2030,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="138">
       <c r="A24" s="3" t="s">
         <v>124</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="111.75">
       <c r="A25" s="3" t="s">
         <v>129</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="45.75">
       <c r="A26" s="3" t="s">
         <v>134</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="111.75">
       <c r="A27" s="3" t="s">
         <v>139</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="150.75">
       <c r="A28" s="3" t="s">
         <v>144</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="111.75">
       <c r="A29" s="3" t="s">
         <v>149</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="111.75">
       <c r="A30" s="3" t="s">
         <v>154</v>
       </c>
